--- a/data/gravel/Viral Wanderer 2025.xlsx
+++ b/data/gravel/Viral Wanderer 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C51E5B-E32C-C84F-84DF-AD91DA326483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D329EB-FD87-1B49-A90A-AC64425ACC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3260" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
   <si>
     <t>brand</t>
   </si>
@@ -333,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -354,18 +354,13 @@
     <font>
       <sz val="15"/>
       <color rgb="FF1A1C18"/>
-      <name val="Font_condensed"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF1A1C18"/>
-      <name val="Font_condensed"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FF1A1C18"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Futura Medium"/>
     </font>
   </fonts>
   <fills count="2">
@@ -388,15 +383,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,13 +688,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +702,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -716,7 +710,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -724,7 +718,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -732,7 +726,7 @@
         <v>45885</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -740,7 +734,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -751,32 +745,32 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="21">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" ht="21">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="6">
@@ -792,11 +786,11 @@
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>82</v>
       </c>
       <c r="C10" s="6">
@@ -812,11 +806,11 @@
         <v>645</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="21">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="6">
@@ -832,11 +826,11 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="21">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C12" s="6">
@@ -852,11 +846,11 @@
         <v>435</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="6">
@@ -872,11 +866,11 @@
         <v>784</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="21">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="6">
@@ -892,11 +886,11 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="21">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C15" s="6">
@@ -912,11 +906,11 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="21">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="6">
@@ -932,11 +926,11 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="21">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C17" s="6">
@@ -952,11 +946,11 @@
         <v>650</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C18" s="6">
@@ -972,11 +966,11 @@
         <v>491</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="21">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C19" s="6">
@@ -992,7 +986,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1002,7 +996,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1029,48 +1023,48 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="21">
+    <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="4">
         <v>44</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="4">
         <v>44</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="4">
         <v>44</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="4">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="5">
         <f>5.25/2.2*1000</f>
         <v>2386.363636363636</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -1090,7 +1084,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1098,7 +1092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -1110,7 +1104,7 @@
         <v>58.419999999999995</v>
       </c>
       <c r="D29">
-        <f t="shared" ref="D29:G29" si="1">2.3*25.4</f>
+        <f t="shared" ref="D29:F29" si="1">2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
       <c r="E29">
@@ -1122,7 +1116,7 @@
         <v>58.419999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1146,7 +1140,7 @@
         <v>183.5</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -1170,7 +1164,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C32">
         <v>160</v>
       </c>
@@ -1184,7 +1178,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1204,7 +1198,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -1212,7 +1206,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -1220,7 +1214,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -1228,7 +1222,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -1236,17 +1230,17 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -1255,12 +1249,12 @@
         <v>58.419999999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -1268,25 +1262,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="B43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -1294,7 +1288,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -1302,17 +1296,17 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -1320,58 +1314,58 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>53</v>
       </c>
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>55</v>
       </c>
@@ -1379,7 +1373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>56</v>
       </c>
@@ -1387,7 +1381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>57</v>
       </c>
@@ -1395,24 +1389,24 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>58</v>
       </c>
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>59</v>
       </c>
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -1420,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>62</v>
       </c>
@@ -1428,17 +1422,17 @@
         <v>6395</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>65</v>
       </c>

--- a/data/gravel/Viral Wanderer 2025.xlsx
+++ b/data/gravel/Viral Wanderer 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D329EB-FD87-1B49-A90A-AC64425ACC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D3B6D4-1D72-E64F-9866-512898C6579B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>titanium</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>external</t>
   </si>
 </sst>
 </file>
@@ -1348,10 +1354,16 @@
       <c r="A57" t="s">
         <v>51</v>
       </c>
+      <c r="B57" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>52</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Viral Wanderer 2025.xlsx
+++ b/data/gravel/Viral Wanderer 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D3B6D4-1D72-E64F-9866-512898C6579B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F65361E-92B8-6F45-9DCD-493F2A4499AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>external</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/5fbd72301fb1862c65651662/1712973587240-WKC14IJKODFXCN4RW0KH/Wanderer+Drive+Side+Profile+SID+SL.jpg?format=2500w</t>
   </si>
 </sst>
 </file>
@@ -740,6 +743,11 @@
         <v>73</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Viral Wanderer 2025.xlsx
+++ b/data/gravel/Viral Wanderer 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F65361E-92B8-6F45-9DCD-493F2A4499AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C6D08F-9A74-374E-B1D1-86F6F1241CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8600" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,15 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/5fbd72301fb1862c65651662/1712973587240-WKC14IJKODFXCN4RW0KH/Wanderer+Drive+Side+Profile+SID+SL.jpg?format=2500w</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bentonville, Arkansas, USA</t>
   </si>
 </sst>
 </file>
@@ -696,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1446,6 +1455,9 @@
       <c r="A69" t="s">
         <v>63</v>
       </c>
+      <c r="B69">
+        <v>9895</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -1456,7 +1468,17 @@
       <c r="A71" t="s">
         <v>65</v>
       </c>
-      <c r="B71" s="1"/>
+      <c r="B71" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Viral Wanderer 2025.xlsx
+++ b/data/gravel/Viral Wanderer 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C6D08F-9A74-374E-B1D1-86F6F1241CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5955653-5873-6B41-BD56-888F217692B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8600" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3260" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,24 @@
   </si>
   <si>
     <t>Bentonville, Arkansas, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -705,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1321,162 +1339,192 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50">
-        <v>30.9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56">
+        <v>30.9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B68" s="1">
-        <v>6395</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69">
-        <v>9895</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>101</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1">
+        <v>6395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>9895</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>102</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>103</v>
       </c>
     </row>

--- a/data/gravel/Viral Wanderer 2025.xlsx
+++ b/data/gravel/Viral Wanderer 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5955653-5873-6B41-BD56-888F217692B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8F664C-2190-6F49-B8D5-2A548AF70B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -248,9 +248,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>a8:f31</t>
-  </si>
-  <si>
     <t>hardtail</t>
   </si>
   <si>
@@ -314,18 +311,9 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>* based on 100 mm travel fork</t>
-  </si>
-  <si>
     <t>suspension</t>
   </si>
   <si>
-    <t>Enve Mountain is 490</t>
-  </si>
-  <si>
-    <t>SID SL with 20% SAG</t>
-  </si>
-  <si>
     <t>titanium</t>
   </si>
   <si>
@@ -363,6 +351,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
+  </si>
+  <si>
+    <t>"* based on 100 mm travel fork"</t>
+  </si>
+  <si>
+    <t>(but there is no indication if this is rigid or sag)</t>
   </si>
 </sst>
 </file>
@@ -723,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -735,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -743,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -767,12 +770,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -780,10 +783,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -791,19 +791,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -812,7 +812,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="6">
         <v>400</v>
@@ -832,7 +832,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="6">
         <v>545</v>
@@ -852,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="6">
         <v>90</v>
@@ -872,7 +872,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="6">
         <v>435</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="6">
         <v>674</v>
@@ -912,7 +912,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="6">
         <v>1098</v>
@@ -932,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="6">
         <v>76.5</v>
@@ -952,7 +952,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="6">
         <v>67.5</v>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="6">
         <v>609</v>
@@ -992,7 +992,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" s="6">
         <v>401</v>
@@ -1012,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" s="6">
         <v>75</v>
@@ -1041,28 +1041,22 @@
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="C21">
-        <f>506 - 0.2*100</f>
-        <v>486</v>
-      </c>
-      <c r="D21">
-        <f t="shared" ref="D21:F21" si="0">506 - 0.2*100</f>
-        <v>486</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>486</v>
+      <c r="C21" s="6">
+        <v>506</v>
+      </c>
+      <c r="D21" s="6">
+        <v>506</v>
+      </c>
+      <c r="E21" s="6">
+        <v>506</v>
+      </c>
+      <c r="F21" s="6">
+        <v>506</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1080,452 +1074,481 @@
       <c r="F22" s="4">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
+      <c r="G22" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4">
+        <v>100</v>
+      </c>
+      <c r="E23" s="4">
+        <v>100</v>
+      </c>
+      <c r="F23" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D28" s="5">
         <f>5.25/2.2*1000</f>
         <v>2386.363636363636</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27">
-        <v>700</v>
-      </c>
-      <c r="D27">
-        <v>700</v>
-      </c>
-      <c r="E27">
-        <v>700</v>
-      </c>
-      <c r="F27">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29">
+        <v>700</v>
+      </c>
+      <c r="D29">
+        <v>700</v>
+      </c>
+      <c r="E29">
+        <v>700</v>
+      </c>
+      <c r="F29">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>26</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <f>2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
-      <c r="D29">
-        <f t="shared" ref="D29:F29" si="1">2.3*25.4</f>
+      <c r="D31">
+        <f t="shared" ref="D31:F31" si="0">2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
-      <c r="E29">
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>58.419999999999995</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>58.419999999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32">
+        <f>C34</f>
+        <v>160</v>
+      </c>
+      <c r="D32">
+        <f>AVERAGE(D34,C35)</f>
+        <v>168.5</v>
+      </c>
+      <c r="E32">
+        <f t="shared" ref="E32:F32" si="1">AVERAGE(E34,D35)</f>
+        <v>176</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="1"/>
-        <v>58.419999999999995</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="1"/>
-        <v>58.419999999999995</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30">
-        <f>C32</f>
-        <v>160</v>
-      </c>
-      <c r="D30">
-        <f>AVERAGE(D32,C33)</f>
+        <v>183.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33">
+        <f>D32</f>
         <v>168.5</v>
       </c>
-      <c r="E30">
-        <f t="shared" ref="E30:F30" si="2">AVERAGE(E32,D33)</f>
+      <c r="D33">
+        <f t="shared" ref="D33:E33" si="2">E32</f>
         <v>176</v>
       </c>
-      <c r="F30">
+      <c r="E33">
         <f t="shared" si="2"/>
         <v>183.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31">
-        <f>D30</f>
-        <v>168.5</v>
-      </c>
-      <c r="D31">
-        <f t="shared" ref="D31:E31" si="3">E30</f>
+      <c r="F33">
+        <f>F35</f>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <v>160</v>
+      </c>
+      <c r="D34">
+        <v>168</v>
+      </c>
+      <c r="E34">
         <v>176</v>
       </c>
-      <c r="E31">
-        <f t="shared" si="3"/>
-        <v>183.5</v>
-      </c>
-      <c r="F31">
-        <f>F33</f>
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C32">
-        <v>160</v>
-      </c>
-      <c r="D32">
-        <v>168</v>
-      </c>
-      <c r="E32">
-        <v>176</v>
-      </c>
-      <c r="F32">
+      <c r="F34">
         <v>184</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33">
-        <v>169</v>
-      </c>
-      <c r="D33">
-        <v>176</v>
-      </c>
-      <c r="E33">
-        <v>183</v>
-      </c>
-      <c r="F33">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>30</v>
+      </c>
+      <c r="C35">
+        <v>169</v>
+      </c>
+      <c r="D35">
+        <v>176</v>
+      </c>
+      <c r="E35">
+        <v>183</v>
+      </c>
+      <c r="F35">
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>67</v>
+      </c>
+      <c r="B37" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>69</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>34</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <f>2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42">
-        <v>100</v>
-      </c>
-    </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="B45" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>40</v>
+      </c>
+      <c r="B48">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>41</v>
+      </c>
+      <c r="B49">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56">
-        <v>30.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <v>30.9</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>53</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>57</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>58</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>59</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>60</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>61</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" s="1">
-        <v>6395</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75">
-        <v>9895</v>
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B76" s="1">
+        <v>6395</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>101</v>
+        <v>63</v>
+      </c>
+      <c r="B77">
+        <v>9895</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>102</v>
-      </c>
-      <c r="B78" t="s">
-        <v>103</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
